--- a/docs/insumos/Metricas_y_Dimensiones.xlsx
+++ b/docs/insumos/Metricas_y_Dimensiones.xlsx
@@ -624,7 +624,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="470">
   <si>
     <t xml:space="preserve">Matriz bus — Data Warehouse I.E. N° 1217 «Jorge Basadre Grohmann»</t>
   </si>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">Matrícula</t>
   </si>
   <si>
-    <t xml:space="preserve">Estudiante + año escolar</t>
+    <t xml:space="preserve">Matrícula — Año</t>
   </si>
   <si>
     <t xml:space="preserve">X (4 roles: solicitud, revisión, asignación, SIAGIE)</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">Preparación curricular</t>
   </si>
   <si>
-    <t xml:space="preserve">Docente + área + sección + año escolar + mes</t>
+    <t xml:space="preserve">Asignación — Mes</t>
   </si>
   <si>
     <t xml:space="preserve">X (mes)</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">Logro por competencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Estudiante + competencia + bimestre</t>
+    <t xml:space="preserve">Calificación — Bimestre</t>
   </si>
   <si>
     <t xml:space="preserve">X (fecha de cierre)</t>
@@ -740,10 +740,7 @@
     <t xml:space="preserve">Se distinguen «no aplica» y «no registrado». Una nota sin evidencia queda vacía, nunca en 0.</t>
   </si>
   <si>
-    <t xml:space="preserve">Grano declarado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nivel temporal de análisis</t>
+    <t xml:space="preserve">Nivel de jerarquía</t>
   </si>
   <si>
     <t xml:space="preserve">Medida</t>
@@ -819,12 +816,6 @@
   </si>
   <si>
     <t xml:space="preserve">Fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una fila = la matrícula de un estudiante en un año escolar, con la sección de ese año. Cuatro roles de fecha: solicitud, revisión, asignación y SIAGIE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Año escolar (día y mes por rol de fecha)</t>
   </si>
   <si>
     <t xml:space="preserve">Matrículas solicitadas</t>
@@ -957,10 +948,7 @@
     <t xml:space="preserve">La matriz anterior lo nombraba en la visualización, no como KPI.</t>
   </si>
   <si>
-    <t xml:space="preserve">Una fila = la preparación de un docente en un área y una sección, por año escolar y mes. Sesiones por mes de clase; material en el mes de entrega (inicio de clases).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mes (bimestre pendiente P1)</t>
+    <t xml:space="preserve">Asignación</t>
   </si>
   <si>
     <t xml:space="preserve">Sesiones programadas</t>
@@ -1069,7 +1057,7 @@
     <t xml:space="preserve">Las entregas sin fecha de recepción no entran al denominador.</t>
   </si>
   <si>
-    <t xml:space="preserve">Una fila = la nota de un estudiante en una competencia, por bimestre (año escolar + bimestre).</t>
+    <t xml:space="preserve">Calificación</t>
   </si>
   <si>
     <t xml:space="preserve">Rendimiento promedio</t>
@@ -1127,7 +1115,7 @@
     <t xml:space="preserve">Estudiantes con nota menor a 11 ÷ estudiantes evaluados</t>
   </si>
   <si>
-    <t xml:space="preserve">Falta definir si basta con un área menor a 11.</t>
+    <t xml:space="preserve">Propuesta P5 (opción 2): bajo rendimiento si alguna área queda menor a 11. Falta que el equipo elija entre las opciones 1 (por competencia), 2 (por área) y 3 (promedio general).</t>
   </si>
   <si>
     <t xml:space="preserve">% de estudiantes aprobados</t>
@@ -2027,13 +2015,22 @@
     <t xml:space="preserve">Modelo v5.2 en SQL Server (DW_IE1217), verificado el 13/10/2026; nombres comprobados contra INFORMATION_SCHEMA.</t>
   </si>
   <si>
+    <t xml:space="preserve">v2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grano por medida, como granularidad: una palabra + nivel de jerarquía (p. ej. Matrícula–Año, Sección–Año, Asignación–Mes, Docente–Mes, Estudiante–Bimestre). Corrige la observación de «% de estudiantes con bajo rendimiento»: «alguna área menor a 11» es la propuesta P5 (opción 2); lo pendiente es elegir entre las opciones 1, 2 y 3. Se crea la versión pública (Drive) sin anotaciones, con estado Script SQL / Power BI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedido del profesor (granularidad) y bitácora (P5).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cómo versionar este archivo</t>
   </si>
   <si>
     <t xml:space="preserve">En Git el archivo conserva su nombre (docs/insumos/Metricas_y_Dimensiones.xlsx); cada cambio es un commit y queda en el historial. Las versiones reemplazadas se guardan en docs/insumos/versiones antiguas.</t>
   </si>
   <si>
-    <t xml:space="preserve">La copia en Google Drive lleva la versión en el nombre (Metricas_y_Dimensiones_v2.0.xlsx) para saber cuál se presentó.</t>
+    <t xml:space="preserve">La copia en Google Drive lleva la versión en el nombre (p. ej. Metricas_y_Dimensiones_v2.1.xlsx) para saber cuál se presentó.</t>
   </si>
   <si>
     <t xml:space="preserve">Corrección menor (texto, una cifra, una fila) → v2.1, v2.2…  Cambio de estructura (hojas, columnas, procesos) → v3.0.</t>
@@ -2710,9 +2707,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="6" style="0" width="15"/>
   </cols>
   <sheetData>
@@ -3035,8 +3030,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36"/>
@@ -3061,22 +3056,22 @@
         <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="J1" s="11" t="s">
         <v>7</v>
@@ -3127,10 +3122,10 @@
       <c r="AJ1" s="20"/>
       <c r="AK1" s="20"/>
       <c r="AL1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM1" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="AM1" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3144,88 +3139,88 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="L2" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="M2" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="N2" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q2" s="21" t="s">
+      <c r="R2" s="21" t="s">
         <v>50</v>
-      </c>
-      <c r="R2" s="21" t="s">
-        <v>51</v>
       </c>
       <c r="S2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="T2" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="U2" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="U2" s="21" t="s">
+      <c r="V2" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="W2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="X2" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y2" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z2" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="W2" s="21" t="s">
+      <c r="AB2" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC2" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD2" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF2" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="X2" s="21" t="s">
+      <c r="AH2" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI2" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ2" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="Y2" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB2" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC2" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE2" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF2" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG2" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="AH2" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI2" s="21" t="s">
+      <c r="AK2" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="AJ2" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK2" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
@@ -3240,48 +3235,48 @@
       <c r="C3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="I3" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="22" t="s">
-        <v>70</v>
-      </c>
       <c r="J3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
@@ -3290,81 +3285,85 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
       <c r="AG3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ3" s="4"/>
       <c r="AK3" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL3" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AM3" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="7"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F4" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
@@ -3373,79 +3372,83 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AE4" s="4"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ4" s="4"/>
       <c r="AK4" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL4" s="6"/>
       <c r="AM4" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
       <c r="B5" s="7"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F5" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
@@ -3454,54 +3457,58 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AE5" s="4"/>
       <c r="AF5" s="4"/>
       <c r="AG5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ5" s="4"/>
       <c r="AK5" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL5" s="6"/>
       <c r="AM5" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="B6" s="7"/>
       <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F6" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -3533,51 +3540,55 @@
       <c r="AK6" s="4"/>
       <c r="AL6" s="6"/>
       <c r="AM6" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
       <c r="B7" s="7"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F7" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
@@ -3586,83 +3597,87 @@
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ7" s="4"/>
       <c r="AK7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL7" s="6"/>
       <c r="AM7" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
       <c r="B8" s="7"/>
       <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F8" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
@@ -3671,83 +3686,87 @@
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AG8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ8" s="4"/>
       <c r="AK8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL8" s="6"/>
       <c r="AM8" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
       <c r="B9" s="7"/>
       <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F9" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
@@ -3756,79 +3775,83 @@
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AC9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AD9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AE9" s="4"/>
       <c r="AF9" s="4"/>
       <c r="AG9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ9" s="4"/>
       <c r="AK9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL9" s="6"/>
       <c r="AM9" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F10" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
@@ -3837,54 +3860,58 @@
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AE10" s="4"/>
       <c r="AF10" s="4"/>
       <c r="AG10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ10" s="4"/>
       <c r="AK10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL10" s="6"/>
       <c r="AM10" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F11" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -3895,13 +3922,13 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
@@ -3916,7 +3943,7 @@
       <c r="AE11" s="4"/>
       <c r="AF11" s="4"/>
       <c r="AG11" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH11" s="4"/>
       <c r="AI11" s="4"/>
@@ -3924,51 +3951,55 @@
       <c r="AK11" s="4"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F12" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
@@ -3977,54 +4008,58 @@
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AC12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AD12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
       <c r="AG12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ12" s="4"/>
       <c r="AK12" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL12" s="6"/>
       <c r="AM12" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F13" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -4035,13 +4070,13 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
@@ -4056,7 +4091,7 @@
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
       <c r="AG13" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH13" s="4"/>
       <c r="AI13" s="4"/>
@@ -4064,7 +4099,7 @@
       <c r="AK13" s="4"/>
       <c r="AL13" s="6"/>
       <c r="AM13" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4077,51 +4112,51 @@
       <c r="C14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>110</v>
+      <c r="D14" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
@@ -4135,70 +4170,74 @@
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
       <c r="AG14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ14" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK14" s="4"/>
       <c r="AL14" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AM14" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="F15" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
@@ -4212,16 +4251,16 @@
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
       <c r="AG15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI15" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ15" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK15" s="4"/>
       <c r="AL15" s="6"/>
@@ -4231,47 +4270,51 @@
       <c r="A16" s="4"/>
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="F16" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
@@ -4285,16 +4328,16 @@
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
       <c r="AG16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI16" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ16" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK16" s="4"/>
       <c r="AL16" s="6"/>
@@ -4304,47 +4347,51 @@
       <c r="A17" s="4"/>
       <c r="B17" s="7"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="F17" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
@@ -4358,68 +4405,72 @@
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
       <c r="AG17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI17" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ17" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK17" s="4"/>
       <c r="AL17" s="6"/>
       <c r="AM17" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
       <c r="B18" s="7"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="F18" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
@@ -4433,68 +4484,72 @@
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
       <c r="AG18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI18" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ18" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK18" s="4"/>
       <c r="AL18" s="6"/>
       <c r="AM18" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
       <c r="B19" s="7"/>
       <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="F19" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -4508,68 +4563,72 @@
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
       <c r="AG19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI19" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ19" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK19" s="4"/>
       <c r="AL19" s="6"/>
       <c r="AM19" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
       <c r="B20" s="7"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="F20" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
@@ -4583,68 +4642,72 @@
       <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
       <c r="AG20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI20" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ20" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK20" s="4"/>
       <c r="AL20" s="6"/>
       <c r="AM20" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
       <c r="B21" s="7"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F21" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
@@ -4658,68 +4721,72 @@
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
       <c r="AG21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI21" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ21" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK21" s="4"/>
       <c r="AL21" s="6"/>
       <c r="AM21" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
       <c r="B22" s="7"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F22" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
@@ -4733,68 +4800,72 @@
       <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
       <c r="AG22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI22" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ22" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK22" s="4"/>
       <c r="AL22" s="6"/>
       <c r="AM22" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
       <c r="B23" s="7"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F23" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
@@ -4808,16 +4879,16 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
       <c r="AG23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI23" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ23" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK23" s="4"/>
       <c r="AL23" s="6"/>
@@ -4827,47 +4898,51 @@
       <c r="A24" s="4"/>
       <c r="B24" s="7"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="F24" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
@@ -4881,21 +4956,21 @@
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
       <c r="AG24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AI24" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AJ24" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AK24" s="4"/>
       <c r="AL24" s="6"/>
       <c r="AM24" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4908,74 +4983,74 @@
       <c r="C25" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>147</v>
+      <c r="D25" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA25" s="4"/>
       <c r="AB25" s="4"/>
@@ -4984,89 +5059,93 @@
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
       <c r="AG25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH25" s="4"/>
       <c r="AI25" s="4"/>
       <c r="AJ25" s="4"/>
       <c r="AK25" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL25" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AM25" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
       <c r="B26" s="7"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="4"/>
+      <c r="D26" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F26" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA26" s="4"/>
       <c r="AB26" s="4"/>
@@ -5075,87 +5154,91 @@
       <c r="AE26" s="4"/>
       <c r="AF26" s="4"/>
       <c r="AG26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH26" s="4"/>
       <c r="AI26" s="4"/>
       <c r="AJ26" s="4"/>
       <c r="AK26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL26" s="6"/>
       <c r="AM26" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
       <c r="B27" s="7"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F27" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA27" s="4"/>
       <c r="AB27" s="4"/>
@@ -5164,87 +5247,91 @@
       <c r="AE27" s="4"/>
       <c r="AF27" s="4"/>
       <c r="AG27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH27" s="4"/>
       <c r="AI27" s="4"/>
       <c r="AJ27" s="4"/>
       <c r="AK27" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL27" s="6"/>
       <c r="AM27" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
       <c r="B28" s="7"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F28" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA28" s="4"/>
       <c r="AB28" s="4"/>
@@ -5253,87 +5340,91 @@
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
       <c r="AG28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH28" s="4"/>
       <c r="AI28" s="4"/>
       <c r="AJ28" s="4"/>
       <c r="AK28" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL28" s="6"/>
       <c r="AM28" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
       <c r="B29" s="7"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="4"/>
+      <c r="D29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F29" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA29" s="4"/>
       <c r="AB29" s="4"/>
@@ -5342,87 +5433,91 @@
       <c r="AE29" s="4"/>
       <c r="AF29" s="4"/>
       <c r="AG29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH29" s="4"/>
       <c r="AI29" s="4"/>
       <c r="AJ29" s="4"/>
       <c r="AK29" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL29" s="6"/>
       <c r="AM29" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
       <c r="B30" s="7"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="4"/>
+      <c r="D30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F30" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA30" s="4"/>
       <c r="AB30" s="4"/>
@@ -5431,87 +5526,91 @@
       <c r="AE30" s="4"/>
       <c r="AF30" s="4"/>
       <c r="AG30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH30" s="4"/>
       <c r="AI30" s="4"/>
       <c r="AJ30" s="4"/>
       <c r="AK30" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL30" s="6"/>
       <c r="AM30" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
       <c r="B31" s="7"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F31" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA31" s="4"/>
       <c r="AB31" s="4"/>
@@ -5520,87 +5619,91 @@
       <c r="AE31" s="4"/>
       <c r="AF31" s="4"/>
       <c r="AG31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH31" s="4"/>
       <c r="AI31" s="4"/>
       <c r="AJ31" s="4"/>
       <c r="AK31" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL31" s="6"/>
       <c r="AM31" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
       <c r="B32" s="7"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="4"/>
+      <c r="D32" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F32" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I32" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA32" s="4"/>
       <c r="AB32" s="4"/>
@@ -5609,87 +5712,91 @@
       <c r="AE32" s="4"/>
       <c r="AF32" s="4"/>
       <c r="AG32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH32" s="4"/>
       <c r="AI32" s="4"/>
       <c r="AJ32" s="4"/>
       <c r="AK32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL32" s="6"/>
       <c r="AM32" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
       <c r="B33" s="7"/>
       <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="F33" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="V33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Y33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Z33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AA33" s="4"/>
       <c r="AB33" s="4"/>
@@ -5698,28 +5805,28 @@
       <c r="AE33" s="4"/>
       <c r="AF33" s="4"/>
       <c r="AG33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AH33" s="4"/>
       <c r="AI33" s="4"/>
       <c r="AJ33" s="4"/>
       <c r="AK33" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="AL33" s="6"/>
       <c r="AM33" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D36" s="28"/>
       <c r="E36" s="28"/>
@@ -5729,10 +5836,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D37" s="28"/>
       <c r="E37" s="28"/>
@@ -5742,10 +5849,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="22" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
@@ -5755,10 +5862,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="26" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="28"/>
@@ -5768,10 +5875,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="23" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D40" s="28"/>
       <c r="E40" s="28"/>
@@ -5781,7 +5888,7 @@
     </row>
     <row r="41" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
@@ -5792,7 +5899,7 @@
     </row>
     <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
@@ -5803,7 +5910,7 @@
     </row>
     <row r="43" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
@@ -5814,7 +5921,7 @@
     </row>
     <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
@@ -5824,7 +5931,7 @@
       <c r="H44" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="40">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5847,20 +5954,14 @@
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="B3:B13"/>
     <mergeCell ref="C3:C13"/>
-    <mergeCell ref="D3:D13"/>
-    <mergeCell ref="E3:E13"/>
     <mergeCell ref="AL3:AL13"/>
     <mergeCell ref="A14:A24"/>
     <mergeCell ref="B14:B24"/>
     <mergeCell ref="C14:C24"/>
-    <mergeCell ref="D14:D24"/>
-    <mergeCell ref="E14:E24"/>
     <mergeCell ref="AL14:AL24"/>
     <mergeCell ref="A25:A33"/>
     <mergeCell ref="B25:B33"/>
     <mergeCell ref="C25:C33"/>
-    <mergeCell ref="D25:D33"/>
-    <mergeCell ref="E25:E33"/>
     <mergeCell ref="AL25:AL33"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="C37:H37"/>
@@ -5912,31 +6013,31 @@
         <v>3</v>
       </c>
       <c r="C1" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="H1" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="I1" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="J1" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="K1" s="29" t="s">
         <v>191</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5944,34 +6045,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="G2" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="H2" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="J2" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="K2" s="30" t="s">
         <v>200</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5979,34 +6080,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E3" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="K3" s="30" t="s">
         <v>205</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="G3" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="H3" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="K3" s="30" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6014,34 +6115,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="G4" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="H4" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="I4" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="J4" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="K4" s="30" t="s">
         <v>215</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="I4" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6049,34 +6150,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D5" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="J5" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="E5" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="G5" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="J5" s="31" t="s">
-        <v>224</v>
-      </c>
       <c r="K5" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6084,34 +6185,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D6" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="J6" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="E6" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="G6" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>229</v>
-      </c>
       <c r="K6" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6119,34 +6220,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6154,34 +6255,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6189,34 +6290,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I9" s="31" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J9" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6224,34 +6325,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C10" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="G10" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="H10" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="I10" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="F10" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>248</v>
-      </c>
       <c r="J10" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6259,34 +6360,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="K11" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6294,34 +6395,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K12" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6329,34 +6430,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C13" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="H13" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="I13" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="J13" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="G13" s="31" t="s">
-        <v>259</v>
-      </c>
-      <c r="H13" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>262</v>
-      </c>
       <c r="K13" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6364,34 +6465,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C14" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="G14" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="H14" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="I14" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="J14" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="G14" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>270</v>
-      </c>
       <c r="K14" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6399,34 +6500,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C15" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="G15" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="H15" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="I15" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="J15" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="G15" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="H15" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>278</v>
-      </c>
       <c r="K15" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6434,34 +6535,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C16" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="I16" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="31" t="s">
+      <c r="J16" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="G16" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="I16" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>284</v>
-      </c>
       <c r="K16" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6469,34 +6570,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C17" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="I17" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="D17" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="31" t="s">
+      <c r="J17" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="G17" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="H17" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="I17" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="J17" s="31" t="s">
-        <v>290</v>
-      </c>
       <c r="K17" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6504,34 +6605,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F18" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="J18" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="G18" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="H18" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="I18" s="31" t="s">
-        <v>294</v>
-      </c>
-      <c r="J18" s="31" t="s">
-        <v>295</v>
-      </c>
       <c r="K18" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6539,34 +6640,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C19" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="G19" s="31" t="s">
         <v>296</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="H19" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="I19" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="J19" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="F19" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>300</v>
-      </c>
-      <c r="H19" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="J19" s="31" t="s">
-        <v>302</v>
-      </c>
       <c r="K19" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6574,34 +6675,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D20" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="I20" s="31" t="s">
         <v>303</v>
       </c>
-      <c r="E20" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="H20" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="I20" s="31" t="s">
-        <v>307</v>
-      </c>
       <c r="J20" s="31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6609,34 +6710,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="H21" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="C21" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="D21" s="33" t="s">
+      <c r="I21" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="E21" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="F21" s="33" t="s">
+      <c r="J21" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="G21" s="33" t="s">
+      <c r="K21" s="32" t="s">
         <v>311</v>
-      </c>
-      <c r="H21" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="I21" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="J21" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="K21" s="32" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6644,34 +6745,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C22" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="G22" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="H22" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="E22" s="33" t="s">
+      <c r="I22" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="F22" s="33" t="s">
+      <c r="J22" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="G22" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="H22" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="I22" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="J22" s="33" t="s">
-        <v>323</v>
-      </c>
       <c r="K22" s="32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6679,34 +6780,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F23" s="33" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H23" s="33" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I23" s="33" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K23" s="32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6714,34 +6815,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D24" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="I24" s="33" t="s">
         <v>328</v>
       </c>
-      <c r="E24" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="F24" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G24" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="H24" s="33" t="s">
-        <v>331</v>
-      </c>
-      <c r="I24" s="33" t="s">
-        <v>332</v>
-      </c>
       <c r="J24" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K24" s="32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6749,34 +6850,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D25" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="I25" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="E25" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="F25" s="33" t="s">
+      <c r="J25" s="33" t="s">
         <v>334</v>
       </c>
-      <c r="G25" s="33" t="s">
-        <v>335</v>
-      </c>
-      <c r="H25" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="I25" s="33" t="s">
-        <v>337</v>
-      </c>
-      <c r="J25" s="33" t="s">
-        <v>338</v>
-      </c>
       <c r="K25" s="32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6784,34 +6885,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F26" s="33" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G26" s="33" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H26" s="33" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="I26" s="33" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K26" s="32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6819,34 +6920,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F27" s="33" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H27" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I27" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J27" s="33" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="K27" s="32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6854,34 +6955,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D28" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>345</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="J28" s="33" t="s">
         <v>347</v>
       </c>
-      <c r="E28" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="F28" s="33" t="s">
-        <v>348</v>
-      </c>
-      <c r="G28" s="33" t="s">
-        <v>349</v>
-      </c>
-      <c r="H28" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="33" t="s">
-        <v>350</v>
-      </c>
-      <c r="J28" s="33" t="s">
-        <v>351</v>
-      </c>
       <c r="K28" s="32" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6889,34 +6990,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>350</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="F29" s="33" t="s">
         <v>352</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="G29" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="H29" s="33" t="s">
         <v>354</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="I29" s="33" t="s">
         <v>355</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="J29" s="33" t="s">
         <v>356</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="K29" s="32" t="s">
         <v>357</v>
-      </c>
-      <c r="H29" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="I29" s="33" t="s">
-        <v>359</v>
-      </c>
-      <c r="J29" s="33" t="s">
-        <v>360</v>
-      </c>
-      <c r="K29" s="32" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6924,34 +7025,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C30" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>360</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="G30" s="33" t="s">
         <v>362</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="H30" s="33" t="s">
         <v>363</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="I30" s="33" t="s">
         <v>364</v>
       </c>
-      <c r="F30" s="33" t="s">
+      <c r="J30" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="G30" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="H30" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>368</v>
-      </c>
-      <c r="J30" s="33" t="s">
-        <v>369</v>
-      </c>
       <c r="K30" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6959,34 +7060,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F31" s="33" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="G31" s="33" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="H31" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I31" s="33" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K31" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6994,34 +7095,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F32" s="33" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="G32" s="33" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="H32" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I32" s="33" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K32" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7029,34 +7130,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F33" s="33" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="H33" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="J33" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K33" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7064,34 +7165,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F34" s="33" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G34" s="33" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="H34" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I34" s="33" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K34" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7099,34 +7200,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C35" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>383</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="G35" s="33" t="s">
         <v>386</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="H35" s="33" t="s">
         <v>387</v>
       </c>
-      <c r="E35" s="33" t="s">
+      <c r="I35" s="33" t="s">
         <v>388</v>
       </c>
-      <c r="F35" s="33" t="s">
+      <c r="J35" s="33" t="s">
         <v>389</v>
       </c>
-      <c r="G35" s="33" t="s">
-        <v>390</v>
-      </c>
-      <c r="H35" s="33" t="s">
-        <v>391</v>
-      </c>
-      <c r="I35" s="33" t="s">
-        <v>392</v>
-      </c>
-      <c r="J35" s="33" t="s">
-        <v>393</v>
-      </c>
       <c r="K35" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7134,34 +7235,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C36" s="33" t="s">
+        <v>390</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>391</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>392</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>393</v>
+      </c>
+      <c r="G36" s="33" t="s">
         <v>394</v>
       </c>
-      <c r="D36" s="33" t="s">
+      <c r="H36" s="33" t="s">
         <v>395</v>
       </c>
-      <c r="E36" s="33" t="s">
+      <c r="I36" s="33" t="s">
         <v>396</v>
       </c>
-      <c r="F36" s="33" t="s">
+      <c r="J36" s="33" t="s">
         <v>397</v>
       </c>
-      <c r="G36" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H36" s="33" t="s">
-        <v>399</v>
-      </c>
-      <c r="I36" s="33" t="s">
-        <v>400</v>
-      </c>
-      <c r="J36" s="33" t="s">
-        <v>401</v>
-      </c>
       <c r="K36" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7169,34 +7270,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D37" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>400</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="I37" s="33" t="s">
+        <v>401</v>
+      </c>
+      <c r="J37" s="33" t="s">
         <v>402</v>
       </c>
-      <c r="E37" s="33" t="s">
-        <v>388</v>
-      </c>
-      <c r="F37" s="33" t="s">
-        <v>403</v>
-      </c>
-      <c r="G37" s="33" t="s">
-        <v>404</v>
-      </c>
-      <c r="H37" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I37" s="33" t="s">
-        <v>405</v>
-      </c>
-      <c r="J37" s="33" t="s">
-        <v>406</v>
-      </c>
       <c r="K37" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7204,34 +7305,34 @@
         <v>37</v>
       </c>
       <c r="B38" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="F38" s="33" t="s">
         <v>407</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="G38" s="33" t="s">
         <v>408</v>
       </c>
-      <c r="D38" s="33" t="s">
+      <c r="H38" s="33" t="s">
         <v>409</v>
       </c>
-      <c r="E38" s="33" t="s">
+      <c r="I38" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="F38" s="33" t="s">
+      <c r="J38" s="33" t="s">
         <v>411</v>
       </c>
-      <c r="G38" s="33" t="s">
+      <c r="K38" s="32" t="s">
         <v>412</v>
-      </c>
-      <c r="H38" s="33" t="s">
-        <v>413</v>
-      </c>
-      <c r="I38" s="33" t="s">
-        <v>414</v>
-      </c>
-      <c r="J38" s="33" t="s">
-        <v>415</v>
-      </c>
-      <c r="K38" s="32" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7239,34 +7340,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D39" s="33" t="s">
+        <v>413</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>414</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>415</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="I39" s="33" t="s">
         <v>417</v>
       </c>
-      <c r="E39" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="F39" s="33" t="s">
-        <v>418</v>
-      </c>
-      <c r="G39" s="33" t="s">
-        <v>419</v>
-      </c>
-      <c r="H39" s="33" t="s">
-        <v>420</v>
-      </c>
-      <c r="I39" s="33" t="s">
-        <v>421</v>
-      </c>
       <c r="J39" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K39" s="32" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7274,34 +7375,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D40" s="33" t="s">
+        <v>418</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>420</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="I40" s="33" t="s">
         <v>422</v>
       </c>
-      <c r="E40" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="F40" s="33" t="s">
+      <c r="J40" s="33" t="s">
         <v>423</v>
       </c>
-      <c r="G40" s="33" t="s">
-        <v>424</v>
-      </c>
-      <c r="H40" s="33" t="s">
-        <v>425</v>
-      </c>
-      <c r="I40" s="33" t="s">
-        <v>426</v>
-      </c>
-      <c r="J40" s="33" t="s">
-        <v>427</v>
-      </c>
       <c r="K40" s="32" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7309,34 +7410,34 @@
         <v>40</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C41" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>425</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>427</v>
+      </c>
+      <c r="H41" s="33" t="s">
         <v>428</v>
       </c>
-      <c r="D41" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="E41" s="33" t="s">
+      <c r="I41" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="F41" s="33" t="s">
-        <v>430</v>
-      </c>
-      <c r="G41" s="33" t="s">
-        <v>431</v>
-      </c>
-      <c r="H41" s="33" t="s">
-        <v>432</v>
-      </c>
-      <c r="I41" s="33" t="s">
-        <v>433</v>
-      </c>
       <c r="J41" s="33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K41" s="32" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7344,34 +7445,34 @@
         <v>41</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D42" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>432</v>
+      </c>
+      <c r="H42" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="J42" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="E42" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="F42" s="33" t="s">
-        <v>435</v>
-      </c>
-      <c r="G42" s="33" t="s">
-        <v>436</v>
-      </c>
-      <c r="H42" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="I42" s="33" t="s">
-        <v>437</v>
-      </c>
-      <c r="J42" s="33" t="s">
-        <v>438</v>
-      </c>
       <c r="K42" s="32" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7379,34 +7480,34 @@
         <v>42</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D43" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>437</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="I43" s="33" t="s">
         <v>439</v>
       </c>
-      <c r="E43" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="F43" s="33" t="s">
+      <c r="J43" s="33" t="s">
         <v>440</v>
       </c>
-      <c r="G43" s="33" t="s">
-        <v>441</v>
-      </c>
-      <c r="H43" s="33" t="s">
-        <v>442</v>
-      </c>
-      <c r="I43" s="33" t="s">
-        <v>443</v>
-      </c>
-      <c r="J43" s="33" t="s">
-        <v>444</v>
-      </c>
       <c r="K43" s="32" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7414,34 +7515,34 @@
         <v>43</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D44" s="33" t="s">
+        <v>441</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>442</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>443</v>
+      </c>
+      <c r="H44" s="33" t="s">
+        <v>444</v>
+      </c>
+      <c r="I44" s="33" t="s">
         <v>445</v>
       </c>
-      <c r="E44" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="F44" s="33" t="s">
+      <c r="J44" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="G44" s="33" t="s">
-        <v>447</v>
-      </c>
-      <c r="H44" s="33" t="s">
-        <v>448</v>
-      </c>
-      <c r="I44" s="33" t="s">
-        <v>449</v>
-      </c>
-      <c r="J44" s="33" t="s">
-        <v>450</v>
-      </c>
       <c r="K44" s="32" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -7463,7 +7564,7 @@
     <tabColor rgb="FF999999"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -7475,82 +7576,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>454</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" s="33" t="s">
         <v>456</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>457</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>458</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>459</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>460</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>461</v>
       </c>
-      <c r="B5" s="33" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="s">
         <v>462</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="B6" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>463</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="E6" s="33" t="s">
         <v>464</v>
       </c>
-      <c r="E5" s="33" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="27" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>467</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
@@ -7561,7 +7668,7 @@
         <v>33</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
@@ -7572,18 +7679,29 @@
         <v>33</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
       <c r="E12" s="28"/>
     </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
